--- a/data/trans_bre/P16A04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,22</t>
+          <t>-1,96; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,74</t>
+          <t>-0,47; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,65</t>
+          <t>0,33; 3,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,26</t>
+          <t>-2,72; 3,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 148,58</t>
+          <t>-73,17; 131,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 353,89</t>
+          <t>-22,06; 329,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 1540,02</t>
+          <t>-9,86; 1541,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-92,12; 658,49</t>
+          <t>-94,54; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,19</t>
+          <t>0,43; 3,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,86</t>
+          <t>-0,57; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,12</t>
+          <t>-2,52; 1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,02</t>
+          <t>-0,66; 2,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 716,31</t>
+          <t>10,98; 652,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 211,13</t>
+          <t>-19,72; 210,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 57,31</t>
+          <t>-62,33; 62,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 5479,95</t>
+          <t>-57,86; 6314,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,73</t>
+          <t>0,15; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,87</t>
+          <t>-1,45; 2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,49</t>
+          <t>-1,62; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,98</t>
+          <t>-1,59; 2,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 864,07</t>
+          <t>-4,03; 988,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 127,07</t>
+          <t>-47,58; 137,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 113,12</t>
+          <t>-55,62; 106,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 137,41</t>
+          <t>-45,24; 139,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,29</t>
+          <t>-1,84; 1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,13</t>
+          <t>-1,95; 1,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,15</t>
+          <t>-2,53; 0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,39</t>
+          <t>-0,53; 4,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,65; 187,02</t>
+          <t>-72,45; 157,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 103,43</t>
+          <t>-67,84; 135,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,64; 35,08</t>
+          <t>-89,62; 33,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 432,41</t>
+          <t>-18,09; 383,14</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,34</t>
+          <t>-3,42; 1,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,82</t>
+          <t>-3,88; 0,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,89</t>
+          <t>-0,84; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,06</t>
+          <t>-0,35; 3,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 74,44</t>
+          <t>-74,31; 81,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 59,58</t>
+          <t>-82,09; 50,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 385,28</t>
+          <t>-35,77; 307,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 205,87</t>
+          <t>-9,68; 186,51</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,33</t>
+          <t>-2,38; 2,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,2</t>
+          <t>-7,41; 0,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,94</t>
+          <t>-3,08; 2,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,54</t>
+          <t>-2,9; 1,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 134,62</t>
+          <t>-55,92; 160,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 12,43</t>
+          <t>-82,59; 22,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 176,48</t>
+          <t>-75,37; 174,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 72,79</t>
+          <t>-72,6; 80,45</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,38</t>
+          <t>-4,34; 2,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 2,57</t>
+          <t>-4,33; 2,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,23</t>
+          <t>0,27; 4,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,64</t>
+          <t>-0,61; 3,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 130,99</t>
+          <t>-75,72; 163,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-69,27; 129,12</t>
+          <t>-69,7; 117,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,82; —</t>
+          <t>-30,22; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 208,73</t>
+          <t>-16,93; 207,79</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,2</t>
+          <t>-0,25; 1,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,88</t>
+          <t>-0,91; 0,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,98</t>
+          <t>-0,45; 1,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,81</t>
+          <t>0,11; 1,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 80,16</t>
+          <t>-12,04; 76,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 37,74</t>
+          <t>-27,9; 35,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 55,63</t>
+          <t>-19,66; 59,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 106,98</t>
+          <t>4,36; 107,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,38</t>
+          <t>-2,19; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,71</t>
+          <t>-0,59; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,78</t>
+          <t>0,29; 3,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,52</t>
+          <t>-2,42; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 131,73</t>
+          <t>-74,43; 162,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 329,73</t>
+          <t>-33,56; 335,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 1541,66</t>
+          <t>-8,27; 1470,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-94,54; —</t>
+          <t>-82,15; 857,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130,5%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,27</t>
+          <t>0,35; 3,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,12</t>
+          <t>-0,41; 3,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,21</t>
+          <t>-2,67; 1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,99</t>
+          <t>-1,23; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 652,82</t>
+          <t>9,17; 714,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 210,32</t>
+          <t>-17,2; 199,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,33; 62,24</t>
+          <t>-61,02; 59,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 6314,26</t>
+          <t>-64,03; 989,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,75</t>
+          <t>-0,01; 2,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,11</t>
+          <t>-1,3; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,48</t>
+          <t>-1,66; 1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,11</t>
+          <t>-1,06; 2,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 988,0</t>
+          <t>-16,16; 777,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 137,64</t>
+          <t>-46,2; 130,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 106,85</t>
+          <t>-56,93; 123,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 139,53</t>
+          <t>-36,15; 177,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>-2,7%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,24</t>
+          <t>-1,95; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,33</t>
+          <t>-2,21; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,15</t>
+          <t>-2,58; 0,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,28</t>
+          <t>-2,01; 1,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 157,8</t>
+          <t>-77,65; 152,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 135,8</t>
+          <t>-74,14; 92,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 33,13</t>
+          <t>-90,86; 40,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 383,14</t>
+          <t>-49,15; 82,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,4</t>
+          <t>-3,45; 1,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,77</t>
+          <t>-3,76; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,59</t>
+          <t>-0,93; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,01</t>
+          <t>0,02; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 81,95</t>
+          <t>-73,17; 65,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-82,09; 50,17</t>
+          <t>-77,82; 73,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 307,55</t>
+          <t>-33,02; 304,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 186,51</t>
+          <t>-2,05; 213,92</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,08%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,39</t>
+          <t>-2,85; 2,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,35</t>
+          <t>-7,31; 0,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,11</t>
+          <t>-2,91; 2,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,65</t>
+          <t>-0,84; 2,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,92; 160,19</t>
+          <t>-63,06; 134,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 22,29</t>
+          <t>-82,09; 18,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,37; 174,56</t>
+          <t>-73,72; 187,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 80,45</t>
+          <t>-25,11; 170,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,67</t>
+          <t>-4,46; 2,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,4</t>
+          <t>-5,02; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,19</t>
+          <t>0,03; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,82</t>
+          <t>-0,92; 3,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-75,72; 163,84</t>
+          <t>-72,25; 127,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 117,18</t>
+          <t>-74,1; 96,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,22; —</t>
+          <t>-37,93; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 207,79</t>
+          <t>-23,38; 223,88</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,1</t>
+          <t>-0,29; 1,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,86</t>
+          <t>-0,86; 0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,01</t>
+          <t>-0,47; 0,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,82</t>
+          <t>0,23; 1,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 76,57</t>
+          <t>-14,59; 76,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 35,43</t>
+          <t>-24,93; 39,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,52</t>
+          <t>-20,1; 58,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 107,77</t>
+          <t>7,87; 88,51</t>
         </is>
       </c>
     </row>
